--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484763_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484763_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5653</v>
+        <v>6.9453</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5562</v>
+        <v>5.7511</v>
       </c>
       <c r="F2" t="n">
-        <v>1.009</v>
+        <v>1.1942</v>
       </c>
       <c r="G2" t="n">
         <v>2.5786</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3715</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5139</v>
+        <v>-0.319</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1423</v>
+        <v>0.3275</v>
       </c>
       <c r="V2" t="n">
         <v>4.3582</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4166</v>
+        <v>5.8082</v>
       </c>
       <c r="E3" t="n">
         <v>2.294</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1227</v>
+        <v>3.5142</v>
       </c>
       <c r="G3" t="n">
         <v>3.1094</v>
@@ -688,13 +688,13 @@
         <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8166</v>
+        <v>0.2081</v>
       </c>
       <c r="T3" t="n">
         <v>-0.5014999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3181</v>
+        <v>0.7096</v>
       </c>
       <c r="V3" t="n">
         <v>0.6036</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7334</v>
+        <v>3.0522</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8967</v>
+        <v>3.189</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1632</v>
+        <v>-0.1368</v>
       </c>
       <c r="G4" t="n">
         <v>4.5664</v>
@@ -766,13 +766,13 @@
         <v>0.7548</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0217</v>
+        <v>-0.7029</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.5772</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1522</v>
+        <v>-0.1257</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6226</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0764</v>
+        <v>1.9164</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8349</v>
+        <v>1.5426</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2415</v>
+        <v>0.3738</v>
       </c>
       <c r="G5" t="n">
         <v>2.4271</v>
@@ -844,13 +844,13 @@
         <v>0.9435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5737</v>
+        <v>0.4137</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4267</v>
+        <v>0.1344</v>
       </c>
       <c r="U5" t="n">
-        <v>0.147</v>
+        <v>0.2792</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9244</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>D. CAZORLA ZARAGOZI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2635</v>
+        <v>1.774</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4189</v>
+        <v>1.8689</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6824</v>
+        <v>-0.0949</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4202</v>
+        <v>-1.2786</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0808</v>
+        <v>-0.5728</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6606</v>
+        <v>-0.7057</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3368</v>
+        <v>0.3083</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1071</v>
+        <v>0.1268</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4439</v>
+        <v>0.1816</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0834</v>
+        <v>-1.5869</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.188</v>
+        <v>-0.6996</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1045</v>
+        <v>-0.8873</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.3209</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6837</v>
+        <v>0.4864</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5596</v>
+        <v>0.3153</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1241</v>
+        <v>0.1711</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6226</v>
+        <v>1.2452</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CAZORLA ZARAGOZI</t>
+          <t>S. SIDDIQUE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1629</v>
+        <v>1.0039</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2843</v>
+        <v>0.1229</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1214</v>
+        <v>0.881</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2786</v>
+        <v>-1.4195</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5728</v>
+        <v>-2.5129</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7057</v>
+        <v>1.0935</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3083</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1268</v>
+        <v>-1.5206</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1816</v>
+        <v>1.4396</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5869</v>
+        <v>-1.3384</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6996</v>
+        <v>-0.9923</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8873</v>
+        <v>-0.3461</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1246</v>
+        <v>0.6496</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2693</v>
+        <v>0.2039</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1447</v>
+        <v>0.4456</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2452</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. SIDDIQUE</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7922</v>
+        <v>0.8737</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1229</v>
+        <v>-0.8086</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6694</v>
+        <v>1.6824</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4195</v>
+        <v>-0.4202</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.5129</v>
+        <v>-1.0808</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0935</v>
+        <v>0.6606</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.3368</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5206</v>
+        <v>0.1071</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4396</v>
+        <v>-0.4439</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3384</v>
+        <v>-0.0834</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9923</v>
+        <v>-1.188</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3461</v>
+        <v>1.1045</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1322</v>
+        <v>0.3774</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1322</v>
+        <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4379</v>
+        <v>0.2939</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2039</v>
+        <v>0.1698</v>
       </c>
       <c r="U8" t="n">
-        <v>0.234</v>
+        <v>0.1241</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6226</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3344</v>
+        <v>-1.4059</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8333</v>
+        <v>-1.2487</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5011</v>
+        <v>-0.1572</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1667</v>
@@ -1234,13 +1234,13 @@
         <v>1.1322</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6772</v>
+        <v>0.2513</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7984</v>
+        <v>-0.2137</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1211</v>
+        <v>0.465</v>
       </c>
       <c r="V10" t="n">
         <v>0.3208</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.1271</v>
+        <v>-8.418900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.0503</v>
+        <v>-8.0246</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.3943</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0726</v>
@@ -1312,13 +1312,13 @@
         <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0969</v>
+        <v>-0.1949</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2091</v>
+        <v>0.2348</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1122</v>
+        <v>-0.4296</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.6684</v>
+        <v>11.6685</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5101</v>
+        <v>4.510200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>7.158499999999999</v>
+        <v>7.158399999999999</v>
       </c>
       <c r="G12" t="n">
         <v>3.242499999999999</v>
@@ -1372,7 +1372,7 @@
         <v>9.414800000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.187399999999999</v>
+        <v>-6.1874</v>
       </c>
       <c r="N12" t="n">
         <v>-8.788499999999999</v>
@@ -1390,13 +1390,13 @@
         <v>12.2655</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2374</v>
+        <v>1.2373</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7297</v>
+        <v>-0.7296000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9669</v>
+        <v>1.9668</v>
       </c>
       <c r="V12" t="n">
         <v>6.245000000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>M. TAEÑO ELEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3826</v>
+        <v>1.2509</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1871</v>
+        <v>1.2509</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1955</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2452</v>
+        <v>1.2509</v>
       </c>
       <c r="H13" t="n">
-        <v>1.94</v>
+        <v>0.6339</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6949</v>
+        <v>0.617</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6688</v>
+        <v>1.2509</v>
       </c>
       <c r="K13" t="n">
-        <v>1.195</v>
+        <v>0.6339</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5262</v>
+        <v>0.617</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4236</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7451</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1687</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4766</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5183</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9583</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8488</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. TAEÑO ELEZ</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2509</v>
+        <v>0.7938</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2509</v>
+        <v>0.9204</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0.1267</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2509</v>
+        <v>0.2452</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6339</v>
+        <v>1.94</v>
       </c>
       <c r="I14" t="n">
-        <v>0.617</v>
+        <v>-1.6949</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2509</v>
+        <v>0.6688</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6339</v>
+        <v>1.195</v>
       </c>
       <c r="L14" t="n">
-        <v>0.617</v>
+        <v>-0.5262</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-0.4236</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.7451</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-1.1687</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.8878</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.2516</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.6361</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.8488</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="15">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2538</v>
+        <v>0.3609</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.768</v>
+        <v>-1.2809</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5142</v>
+        <v>1.6418</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6947</v>
@@ -1702,13 +1702,13 @@
         <v>1.3209</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2522</v>
+        <v>0.8669</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1858</v>
+        <v>0.3014</v>
       </c>
       <c r="U16" t="n">
-        <v>0.438</v>
+        <v>0.5656</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. TAENO ELEZ</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2987</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6053</v>
+        <v>-0.7005</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3066</v>
+        <v>0.7773</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0848</v>
+        <v>-1.4985</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4229</v>
+        <v>0.0775</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3381</v>
+        <v>-1.576</v>
       </c>
       <c r="J17" t="n">
-        <v>2.931</v>
+        <v>-0.2841</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2303</v>
+        <v>0.2747</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7007</v>
+        <v>-0.5588</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8462</v>
+        <v>-1.2144</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1926</v>
+        <v>-0.1972</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0388</v>
+        <v>-1.0172</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.8305</v>
+        <v>1.1322</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.9062</v>
+        <v>-0.1887</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0757</v>
+        <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>0.485</v>
+        <v>0.4431</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4079</v>
+        <v>-0.2277</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0771</v>
+        <v>0.6708</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.038</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.038</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>M. TAENO ELEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6428</v>
+        <v>-0.3553</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1927</v>
+        <v>-1.8976</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4501</v>
+        <v>1.5423</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9641999999999999</v>
+        <v>2.0848</v>
       </c>
       <c r="H18" t="n">
-        <v>1.555</v>
+        <v>2.4229</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5909</v>
+        <v>-0.3381</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4266</v>
+        <v>2.931</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3032</v>
+        <v>2.2303</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1234</v>
+        <v>0.7007</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4624</v>
+        <v>-0.8462</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7482</v>
+        <v>0.1926</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7143</v>
+        <v>-1.0388</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3209</v>
+        <v>-2.8305</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0757</v>
+        <v>-4.9062</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7548</v>
+        <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0347</v>
+        <v>0.4284</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2228</v>
+        <v>0.1156</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2575</v>
+        <v>0.3128</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3208</v>
+        <v>-0.038</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3208</v>
+        <v>-0.038</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7255</v>
+        <v>-0.6187</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1877</v>
+        <v>-0.1927</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4622</v>
+        <v>-0.426</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4985</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0775</v>
+        <v>1.555</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.576</v>
+        <v>-0.5909</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2841</v>
+        <v>2.4266</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2747</v>
+        <v>2.3032</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5588</v>
+        <v>0.1234</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2144</v>
+        <v>-1.4624</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1972</v>
+        <v>-0.7482</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0172</v>
+        <v>-0.7143</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1322</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3592</v>
+        <v>0.0588</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7149</v>
+        <v>-0.2228</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3557</v>
+        <v>0.2816</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5703</v>
+        <v>-1.1926</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6284</v>
+        <v>0.8233</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1987</v>
+        <v>-2.0159</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0417</v>
@@ -2014,13 +2014,13 @@
         <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0381</v>
+        <v>-0.6604</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5879</v>
+        <v>-0.393</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4503</v>
+        <v>-0.2674</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6226</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. MAS GANDIA</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8686</v>
+        <v>-1.3408</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0023</v>
+        <v>1.2335</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8663</v>
+        <v>-2.5743</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4565</v>
+        <v>2.0849</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8937</v>
+        <v>2.0418</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5628</v>
+        <v>0.0431</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6496</v>
+        <v>2.5571</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6496</v>
+        <v>1.2154</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.3417</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8069</v>
+        <v>-0.4721</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2442</v>
+        <v>0.8265</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5628</v>
+        <v>-1.2986</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4121</v>
+        <v>0.3665</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3527</v>
+        <v>0.1295</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0594</v>
+        <v>0.237</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-3.4148</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-4.0374</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>R. MAS GANDIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9542</v>
+        <v>-1.6329</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0386</v>
+        <v>-1.0023</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9928</v>
+        <v>-0.6306</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0849</v>
+        <v>-1.4565</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0418</v>
+        <v>-0.8937</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0431</v>
+        <v>-0.5628</v>
       </c>
       <c r="J22" t="n">
-        <v>2.5571</v>
+        <v>-0.6496</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2154</v>
+        <v>-0.6496</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3417</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4721</v>
+        <v>-0.8069</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8265</v>
+        <v>-0.2442</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2986</v>
+        <v>-0.5628</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2469</v>
+        <v>-0.1764</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0653</v>
+        <v>-0.3527</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1816</v>
+        <v>0.1764</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.4148</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.0374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6944</v>
+        <v>-2.319</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5918</v>
+        <v>-2.3969</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1026</v>
+        <v>0.0779</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7321</v>
@@ -2248,13 +2248,13 @@
         <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9623</v>
+        <v>-0.587</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5879</v>
+        <v>-0.393</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3744</v>
+        <v>-0.194</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9277</v>
+        <v>-5.3768</v>
       </c>
       <c r="E24" t="n">
         <v>-4.5496</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3781</v>
+        <v>-0.8273</v>
       </c>
       <c r="G24" t="n">
         <v>-4.083</v>
@@ -2326,13 +2326,13 @@
         <v>0.5661</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4673</v>
+        <v>-0.9165</v>
       </c>
       <c r="T24" t="n">
         <v>-1.1758</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2915</v>
+        <v>0.2593</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.6686</v>
+        <v>-9.719799999999999</v>
       </c>
       <c r="E25" t="n">
         <v>-7.1585</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.5101</v>
+        <v>-2.5615</v>
       </c>
       <c r="G25" t="n">
         <v>-3.2426</v>
@@ -2392,7 +2392,7 @@
         <v>-0.01529999999999987</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.414700000000002</v>
+        <v>-9.4147</v>
       </c>
       <c r="P25" t="n">
         <v>-0.9434999999999993</v>
@@ -2404,13 +2404,13 @@
         <v>11.322</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.237400000000001</v>
+        <v>0.7111999999999997</v>
       </c>
       <c r="T25" t="n">
         <v>-1.9669</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7294000000000002</v>
+        <v>2.6782</v>
       </c>
       <c r="V25" t="n">
         <v>-6.245</v>
